--- a/etf_holdings/2026-09-02_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:54</t>
+          <t>2026-09-02 01:21:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:54</t>
+          <t>2026-09-02 01:21:09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:54</t>
+          <t>2026-09-02 01:21:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:54</t>
+          <t>2026-09-02 01:21:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:54</t>
+          <t>2026-09-02 01:21:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:54</t>
+          <t>2026-09-02 01:21:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:54</t>
+          <t>2026-09-02 01:21:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:54</t>
+          <t>2026-09-02 01:21:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:54</t>
+          <t>2026-09-02 01:21:09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:54</t>
+          <t>2026-09-02 01:21:09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:54</t>
+          <t>2026-09-02 01:21:09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:54</t>
+          <t>2026-09-02 01:21:09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:54</t>
+          <t>2026-09-02 01:21:09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:54</t>
+          <t>2026-09-02 01:21:09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:54</t>
+          <t>2026-09-02 01:21:09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:55</t>
+          <t>2026-09-02 01:21:10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:55</t>
+          <t>2026-09-02 01:21:10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:55</t>
+          <t>2026-09-02 01:21:10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:55</t>
+          <t>2026-09-02 01:21:10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:55</t>
+          <t>2026-09-02 01:21:10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:55</t>
+          <t>2026-09-02 01:21:10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:55</t>
+          <t>2026-09-02 01:21:10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:55</t>
+          <t>2026-09-02 01:21:10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:55</t>
+          <t>2026-09-02 01:21:10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:55</t>
+          <t>2026-09-02 01:21:10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:55</t>
+          <t>2026-09-02 01:21:10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:55</t>
+          <t>2026-09-02 01:21:10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:55</t>
+          <t>2026-09-02 01:21:10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:55</t>
+          <t>2026-09-02 01:21:10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:55</t>
+          <t>2026-09-02 01:21:10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:56</t>
+          <t>2026-09-02 01:21:11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:56</t>
+          <t>2026-09-02 01:21:11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:56</t>
+          <t>2026-09-02 01:21:11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:56</t>
+          <t>2026-09-02 01:21:11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:56</t>
+          <t>2026-09-02 01:21:11</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:56</t>
+          <t>2026-09-02 01:21:11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:56</t>
+          <t>2026-09-02 01:21:11</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:56</t>
+          <t>2026-09-02 01:21:11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:56</t>
+          <t>2026-09-02 01:21:11</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:56</t>
+          <t>2026-09-02 01:21:11</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:56</t>
+          <t>2026-09-02 01:21:11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:56</t>
+          <t>2026-09-02 01:21:11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:56</t>
+          <t>2026-09-02 01:21:11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:56</t>
+          <t>2026-09-02 01:21:11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:56</t>
+          <t>2026-09-02 01:21:11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:57</t>
+          <t>2026-09-02 01:21:13</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:57</t>
+          <t>2026-09-02 01:21:13</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:57</t>
+          <t>2026-09-02 01:21:13</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:57</t>
+          <t>2026-09-02 01:21:13</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-02 00:34:57</t>
+          <t>2026-09-02 01:21:13</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-02_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:09</t>
+          <t>2026-09-02 16:25:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.46%2440</t>
+          <t>-2.25%2385</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>-2.25%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2440</v>
+        <v>2385</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:09</t>
+          <t>2026-09-02 16:25:09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+2.83%5640</t>
+          <t>-3.46%5445</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5640</v>
+        <v>5445</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:09</t>
+          <t>2026-09-02 16:25:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,12 +631,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-4.6%518</t>
+          <t>0%518</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:09</t>
+          <t>2026-09-02 16:25:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.21%14150</t>
+          <t>-2.01%13865</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-2.01%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>14150</v>
+        <v>13865</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:09</t>
+          <t>2026-09-02 16:25:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-2.8%971</t>
+          <t>+0.21%973</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:09</t>
+          <t>2026-09-02 16:25:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+9.94%7800</t>
+          <t>0%2610</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>7800</v>
+        <v>2610</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:09</t>
+          <t>2026-09-02 16:25:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.44%3410</t>
+          <t>-2.93%3310</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>-2.93%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3410</v>
+        <v>3310</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:09</t>
+          <t>2026-09-02 16:25:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+4.22%568</t>
+          <t>-4.93%540</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+4.22%</t>
+          <t>-4.93%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>568</v>
+        <v>540</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:09</t>
+          <t>2026-09-02 16:25:09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.41%1225</t>
+          <t>-2.04%1200</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1225</v>
+        <v>1200</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:09</t>
+          <t>2026-09-02 16:25:09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+9.94%4315</t>
+          <t>-0.93%4275</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4315</v>
+        <v>4275</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:09</t>
+          <t>2026-09-02 16:25:09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+6.72%874</t>
+          <t>-3.09%847</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+6.72%</t>
+          <t>-3.09%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>874</v>
+        <v>847</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:09</t>
+          <t>2026-09-02 16:25:09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+8.35%2205</t>
+          <t>-2.95%2140</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+8.35%</t>
+          <t>-2.95%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2205</v>
+        <v>2140</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:09</t>
+          <t>2026-09-02 16:25:09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-2.97%3425</t>
+          <t>-0.88%3395</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-2.97%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3425</v>
+        <v>3395</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:09</t>
+          <t>2026-09-02 16:25:09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+1.05%1450</t>
+          <t>-2.76%1410</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+1.05%</t>
+          <t>-2.76%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1450</v>
+        <v>1410</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:09</t>
+          <t>2026-09-02 16:25:09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+6.57%17120</t>
+          <t>+3.53%17725</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+6.57%</t>
+          <t>+3.53%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>17120</v>
+        <v>17725</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:10</t>
+          <t>2026-09-02 16:25:10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,16 +1424,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+5.46%5410</t>
+          <t>-2.22%5290</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+5.46%</t>
+          <t>-2.22%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5410</v>
+        <v>5290</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:10</t>
+          <t>2026-09-02 16:25:10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,16 +1485,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-1.75%5885</t>
+          <t>-1.95%5770</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5885</v>
+        <v>5770</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:10</t>
+          <t>2026-09-02 16:25:10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-1.48%731</t>
+          <t>-6.16%686</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-1.48%</t>
+          <t>-6.16%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>731</v>
+        <v>686</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:10</t>
+          <t>2026-09-02 16:25:10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,16 +1607,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-1.85%2125</t>
+          <t>-2.82%2065</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-1.85%</t>
+          <t>-2.82%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2125</v>
+        <v>2065</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:10</t>
+          <t>2026-09-02 16:25:10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,16 +1668,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+0.17%5870</t>
+          <t>-2.73%5710</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-2.73%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5870</v>
+        <v>5710</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:10</t>
+          <t>2026-09-02 16:25:10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,16 +1729,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-0.92%7580</t>
+          <t>+3.03%7810</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>+3.03%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>7580</v>
+        <v>7810</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:10</t>
+          <t>2026-09-02 16:25:10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+4.45%610</t>
+          <t>-3.44%589</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+4.45%</t>
+          <t>-3.44%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>610</v>
+        <v>589</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:10</t>
+          <t>2026-09-02 16:25:10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+1.03%342</t>
+          <t>-1.46%337</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-1.46%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:10</t>
+          <t>2026-09-02 16:25:10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,16 +1912,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+2.4%256</t>
+          <t>-1.95%251</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:10</t>
+          <t>2026-09-02 16:25:10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+6.68%2315</t>
+          <t>-6.26%2170</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+6.68%</t>
+          <t>-6.26%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2315</v>
+        <v>2170</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:10</t>
+          <t>2026-09-02 16:25:10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+1.93%238</t>
+          <t>-1.47%234.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+1.93%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>238</v>
+        <v>234.5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:10</t>
+          <t>2026-09-02 16:25:10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,16 +2095,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+3.57%2030</t>
+          <t>-2.71%1975</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+3.57%</t>
+          <t>-2.71%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2030</v>
+        <v>1975</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:10</t>
+          <t>2026-09-02 16:25:10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+1.36%1865</t>
+          <t>-7.24%1730</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>-7.24%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1865</v>
+        <v>1730</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:10</t>
+          <t>2026-09-02 16:25:10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+2.25%182</t>
+          <t>+1.92%185.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+2.25%</t>
+          <t>+1.92%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>182</v>
+        <v>185.5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:10</t>
+          <t>2026-09-02 16:25:10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+1.32%153.5</t>
+          <t>-2.61%149.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+1.32%</t>
+          <t>-2.61%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>153.5</v>
+        <v>149.5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:11</t>
+          <t>2026-09-02 16:25:12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+0.69%145</t>
+          <t>-1.03%143.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>145</v>
+        <v>143.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:11</t>
+          <t>2026-09-02 16:25:12</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+2.71%132.5</t>
+          <t>-4.91%126</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+2.71%</t>
+          <t>-4.91%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>132.5</v>
+        <v>126</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:11</t>
+          <t>2026-09-02 16:25:12</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+1.1%1010</t>
+          <t>0%1010</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:11</t>
+          <t>2026-09-02 16:25:12</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+0.45%111</t>
+          <t>-1.8%109</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:11</t>
+          <t>2026-09-02 16:25:12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+3.19%744</t>
+          <t>0%744</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+3.19%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:11</t>
+          <t>2026-09-02 16:25:12</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+1.99%66.7</t>
+          <t>0%66.7</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+1.99%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:11</t>
+          <t>2026-09-02 16:25:12</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+2.78%66.5</t>
+          <t>+0.15%66.6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+2.78%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>66.5</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:11</t>
+          <t>2026-09-02 16:25:12</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+1.31%503</t>
+          <t>-0.2%502</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+1.31%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:11</t>
+          <t>2026-09-02 16:25:12</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-0.1%48.5</t>
+          <t>+1.03%49</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>48.5</v>
+        <v>49</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:11</t>
+          <t>2026-09-02 16:25:12</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+4.54%40.3</t>
+          <t>+2.23%41.2</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+4.54%</t>
+          <t>+2.23%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>40.3</v>
+        <v>41.2</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:11</t>
+          <t>2026-09-02 16:25:12</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+0.97%41.5</t>
+          <t>+1.57%42.15</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>41.5</v>
+        <v>42.15</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:11</t>
+          <t>2026-09-02 16:25:12</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+1.45%41.95</t>
+          <t>+2.5%43</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+2.5%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>41.95</v>
+        <v>43</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:11</t>
+          <t>2026-09-02 16:25:12</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+8.56%279</t>
+          <t>-3.05%270.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+8.56%</t>
+          <t>-3.05%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>279</v>
+        <v>270.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:11</t>
+          <t>2026-09-02 16:25:12</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+0.38%39.9</t>
+          <t>+1.5%40.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>+1.5%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>39.9</v>
+        <v>40.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:11</t>
+          <t>2026-09-02 16:25:12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+3.25%34.95</t>
+          <t>+1.57%35.5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+3.25%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>34.95</v>
+        <v>35.5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:13</t>
+          <t>2026-09-02 16:25:13</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+1.41%252</t>
+          <t>-1.19%249</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+1.41%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:13</t>
+          <t>2026-09-02 16:25:13</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-0.23%216</t>
+          <t>+0.46%217</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.46%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:13</t>
+          <t>2026-09-02 16:25:13</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0%196</t>
+          <t>-4.59%187</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-4.59%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:13</t>
+          <t>2026-09-02 16:25:13</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0%136</t>
+          <t>+1.1%137.5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.1%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>136</v>
+        <v>137.5</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:13</t>
+          <t>2026-09-02 16:25:13</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0%76.2</t>
+          <t>+0.52%76.6</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>76.2</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-09-02_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:09</t>
+          <t>2026-09-02 19:48:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11.19%3,800,000</t>
+          <t>11.23%3,800,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11.19%</t>
+          <t>11.23%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:09</t>
+          <t>2026-09-02 19:48:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9.39%1,380,000</t>
+          <t>9.31%1,380,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.39%</t>
+          <t>9.31%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:09</t>
+          <t>2026-09-02 19:48:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.63%13,800,000</t>
+          <t>8.86%13,800,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.63%</t>
+          <t>8.86%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:09</t>
+          <t>2026-09-02 19:48:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8.54%500,000</t>
+          <t>8.59%500,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8.54%</t>
+          <t>8.59%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:09</t>
+          <t>2026-09-02 19:48:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.86%5,000,000</t>
+          <t>6.03%5,000,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.86%</t>
+          <t>6.03%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:09</t>
+          <t>2026-09-02 19:48:29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -827,16 +827,16 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.46%580,000</t>
+          <t>5.60%1,730,020</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.46%</t>
+          <t>5.60%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>580000</v>
+        <v>1730020</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:09</t>
+          <t>2026-09-02 19:48:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.14%1,250,000</t>
+          <t>5.13%1,250,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.14%</t>
+          <t>5.13%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:09</t>
+          <t>2026-09-02 19:48:29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5.14%7,500,000</t>
+          <t>5.02%7,500,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.14%</t>
+          <t>5.02%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:09</t>
+          <t>2026-09-02 19:48:29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.80%3,250,000</t>
+          <t>4.83%3,250,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.80%</t>
+          <t>4.83%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:09</t>
+          <t>2026-09-02 19:48:29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.69%900,000</t>
+          <t>4.77%900,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.69%</t>
+          <t>4.77%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:09</t>
+          <t>2026-09-02 19:48:29</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.32%4,100,000</t>
+          <t>4.30%4,100,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.32%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:09</t>
+          <t>2026-09-02 19:48:29</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1193,20 +1193,20 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.26%1,600,000</t>
+          <t>3.85%1,450,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4.26%</t>
+          <t>3.85%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1600000</v>
+        <v>1450000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:09</t>
+          <t>2026-09-02 19:48:29</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.72%900,000</t>
+          <t>3.79%900,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.72%</t>
+          <t>3.79%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:09</t>
+          <t>2026-09-02 19:48:29</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1315,20 +1315,20 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.50%2,000,000</t>
+          <t>3.15%1,800,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>2000000</v>
+        <v>1800000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:09</t>
+          <t>2026-09-02 19:48:29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1376,20 +1376,20 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.49%120,500</t>
+          <t>3.09%140,500</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>120500</v>
+        <v>140500</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:10</t>
+          <t>2026-09-02 19:48:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.48%380,000</t>
+          <t>2.49%380,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.49%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:10</t>
+          <t>2026-09-02 19:48:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.41%340,000</t>
+          <t>2.43%340,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.43%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:10</t>
+          <t>2026-09-02 19:48:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.38%2,700,000</t>
+          <t>2.29%2,700,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.29%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:10</t>
+          <t>2026-09-02 19:48:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1620,16 +1620,16 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.26%880,000</t>
+          <t>2.00%780,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>880000</v>
+        <v>780000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:10</t>
+          <t>2026-09-02 19:48:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1681,20 +1681,20 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.13%300,000</t>
+          <t>1.98%280,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>300000</v>
+        <v>280000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:10</t>
+          <t>2026-09-02 19:48:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>0.01%1,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:10</t>
+          <t>2026-09-02 19:48:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:10</t>
+          <t>2026-09-02 19:48:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:10</t>
+          <t>2026-09-02 19:48:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:10</t>
+          <t>2026-09-02 19:48:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,25 +1968,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2603長榮海運</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-6.26%2170</t>
+          <t>-1.47%234.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-6.26%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2170</v>
+        <v>234.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:10</t>
+          <t>2026-09-02 19:48:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,25 +2029,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2603長榮海運</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-1.47%234.5</t>
+          <t>-6.26%2170</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>-6.26%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>234.5</v>
+        <v>2170</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:10</t>
+          <t>2026-09-02 19:48:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:10</t>
+          <t>2026-09-02 19:48:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:10</t>
+          <t>2026-09-02 19:48:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:10</t>
+          <t>2026-09-02 19:48:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:12</t>
+          <t>2026-09-02 19:48:31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:12</t>
+          <t>2026-09-02 19:48:31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:12</t>
+          <t>2026-09-02 19:48:31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:12</t>
+          <t>2026-09-02 19:48:31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:12</t>
+          <t>2026-09-02 19:48:31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:12</t>
+          <t>2026-09-02 19:48:31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:12</t>
+          <t>2026-09-02 19:48:31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:12</t>
+          <t>2026-09-02 19:48:31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:12</t>
+          <t>2026-09-02 19:48:31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:12</t>
+          <t>2026-09-02 19:48:31</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:12</t>
+          <t>2026-09-02 19:48:31</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:12</t>
+          <t>2026-09-02 19:48:31</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:12</t>
+          <t>2026-09-02 19:48:31</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:12</t>
+          <t>2026-09-02 19:48:31</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:12</t>
+          <t>2026-09-02 19:48:31</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:13</t>
+          <t>2026-09-02 19:48:33</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:13</t>
+          <t>2026-09-02 19:48:33</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:13</t>
+          <t>2026-09-02 19:48:33</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:13</t>
+          <t>2026-09-02 19:48:33</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:13</t>
+          <t>2026-09-02 19:48:33</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-02_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:29</t>
+          <t>2026-09-02 22:20:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:29</t>
+          <t>2026-09-02 22:20:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:29</t>
+          <t>2026-09-02 22:20:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:29</t>
+          <t>2026-09-02 22:20:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:29</t>
+          <t>2026-09-02 22:20:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:29</t>
+          <t>2026-09-02 22:20:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:29</t>
+          <t>2026-09-02 22:20:26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:29</t>
+          <t>2026-09-02 22:20:26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:29</t>
+          <t>2026-09-02 22:20:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:29</t>
+          <t>2026-09-02 22:20:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:29</t>
+          <t>2026-09-02 22:20:26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:29</t>
+          <t>2026-09-02 22:20:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:29</t>
+          <t>2026-09-02 22:20:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:29</t>
+          <t>2026-09-02 22:20:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:29</t>
+          <t>2026-09-02 22:20:26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:30</t>
+          <t>2026-09-02 22:20:27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:30</t>
+          <t>2026-09-02 22:20:27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:30</t>
+          <t>2026-09-02 22:20:27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:30</t>
+          <t>2026-09-02 22:20:27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:30</t>
+          <t>2026-09-02 22:20:27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:30</t>
+          <t>2026-09-02 22:20:27</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:30</t>
+          <t>2026-09-02 22:20:27</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:30</t>
+          <t>2026-09-02 22:20:27</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:30</t>
+          <t>2026-09-02 22:20:27</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:30</t>
+          <t>2026-09-02 22:20:27</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:30</t>
+          <t>2026-09-02 22:20:27</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:30</t>
+          <t>2026-09-02 22:20:27</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:30</t>
+          <t>2026-09-02 22:20:27</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:30</t>
+          <t>2026-09-02 22:20:27</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:30</t>
+          <t>2026-09-02 22:20:27</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:31</t>
+          <t>2026-09-02 22:20:28</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:31</t>
+          <t>2026-09-02 22:20:28</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:31</t>
+          <t>2026-09-02 22:20:28</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:31</t>
+          <t>2026-09-02 22:20:28</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:31</t>
+          <t>2026-09-02 22:20:28</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:31</t>
+          <t>2026-09-02 22:20:28</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:31</t>
+          <t>2026-09-02 22:20:28</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:31</t>
+          <t>2026-09-02 22:20:28</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:31</t>
+          <t>2026-09-02 22:20:28</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:31</t>
+          <t>2026-09-02 22:20:28</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:31</t>
+          <t>2026-09-02 22:20:28</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:31</t>
+          <t>2026-09-02 22:20:28</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:31</t>
+          <t>2026-09-02 22:20:28</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:31</t>
+          <t>2026-09-02 22:20:28</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:31</t>
+          <t>2026-09-02 22:20:28</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:33</t>
+          <t>2026-09-02 22:20:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:33</t>
+          <t>2026-09-02 22:20:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:33</t>
+          <t>2026-09-02 22:20:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:33</t>
+          <t>2026-09-02 22:20:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:33</t>
+          <t>2026-09-02 22:20:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-02_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:26</t>
+          <t>2026-09-02 23:15:43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:26</t>
+          <t>2026-09-02 23:15:43</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:26</t>
+          <t>2026-09-02 23:15:43</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:26</t>
+          <t>2026-09-02 23:15:43</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:26</t>
+          <t>2026-09-02 23:15:43</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:26</t>
+          <t>2026-09-02 23:15:43</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:26</t>
+          <t>2026-09-02 23:15:43</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:26</t>
+          <t>2026-09-02 23:15:43</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:26</t>
+          <t>2026-09-02 23:15:43</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:26</t>
+          <t>2026-09-02 23:15:43</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:26</t>
+          <t>2026-09-02 23:15:43</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:26</t>
+          <t>2026-09-02 23:15:43</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:26</t>
+          <t>2026-09-02 23:15:43</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:26</t>
+          <t>2026-09-02 23:15:43</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:26</t>
+          <t>2026-09-02 23:15:43</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:27</t>
+          <t>2026-09-02 23:15:44</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:27</t>
+          <t>2026-09-02 23:15:44</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:27</t>
+          <t>2026-09-02 23:15:44</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:27</t>
+          <t>2026-09-02 23:15:44</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:27</t>
+          <t>2026-09-02 23:15:44</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:27</t>
+          <t>2026-09-02 23:15:44</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:27</t>
+          <t>2026-09-02 23:15:44</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:27</t>
+          <t>2026-09-02 23:15:44</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:27</t>
+          <t>2026-09-02 23:15:44</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:27</t>
+          <t>2026-09-02 23:15:44</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:27</t>
+          <t>2026-09-02 23:15:44</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:27</t>
+          <t>2026-09-02 23:15:44</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:27</t>
+          <t>2026-09-02 23:15:44</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:27</t>
+          <t>2026-09-02 23:15:44</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:27</t>
+          <t>2026-09-02 23:15:44</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:28</t>
+          <t>2026-09-02 23:15:45</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:28</t>
+          <t>2026-09-02 23:15:45</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:28</t>
+          <t>2026-09-02 23:15:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:28</t>
+          <t>2026-09-02 23:15:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:28</t>
+          <t>2026-09-02 23:15:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:28</t>
+          <t>2026-09-02 23:15:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:28</t>
+          <t>2026-09-02 23:15:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:28</t>
+          <t>2026-09-02 23:15:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:28</t>
+          <t>2026-09-02 23:15:45</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:28</t>
+          <t>2026-09-02 23:15:45</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:28</t>
+          <t>2026-09-02 23:15:45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:28</t>
+          <t>2026-09-02 23:15:45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:28</t>
+          <t>2026-09-02 23:15:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:28</t>
+          <t>2026-09-02 23:15:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:28</t>
+          <t>2026-09-02 23:15:45</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:30</t>
+          <t>2026-09-02 23:15:47</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:30</t>
+          <t>2026-09-02 23:15:47</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:30</t>
+          <t>2026-09-02 23:15:47</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:30</t>
+          <t>2026-09-02 23:15:47</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:30</t>
+          <t>2026-09-02 23:15:47</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
